--- a/education_forms/040_simple_seminar_contact_form--education_forms.xlsx
+++ b/education_forms/040_simple_seminar_contact_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -669,7 +669,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>event_time</t>
+          <t>event_time_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Event Time</t>
+          <t>Event Time 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>seminar_date</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Seminar Date</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>seminar_type</t>
+          <t>seminar_type_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seminar Type</t>
+          <t>Seminar Type 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>seminar_date</t>
+          <t>attendees_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seminar Date</t>
+          <t>Attendees 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>event_time</t>
+          <t>seminar_title_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Event Time</t>
+          <t>Seminar Title 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>seminar_title</t>
+          <t>seminar_description_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seminar Title</t>
+          <t>Seminar Description 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>seminar_description</t>
+          <t>seminar_location_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seminar Description</t>
+          <t>Seminar Location 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,115 +975,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>seminar_location</t>
+          <t>event_time_2_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seminar Location</t>
+          <t>Event Time 2 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>attendees</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Attendees</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>registered</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Registered</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Form ID</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,10 +1006,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1245,7 +1153,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>seminar_type_choices</t>
+          <t>seminar_type_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1170,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>seminar_type_choices</t>
+          <t>seminar_type_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1187,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>seminar_type_choices</t>
+          <t>seminar_type_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1204,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>attendees_choices</t>
+          <t>attendees_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1221,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>attendees_choices</t>
+          <t>attendees_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1322,40 +1230,6 @@
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>registered_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>registered_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t>False</t>
         </is>
